--- a/mode_docx_gen/pmi_ka2/ka_modes/КА_33.xlsx
+++ b/mode_docx_gen/pmi_ka2/ka_modes/КА_33.xlsx
@@ -653,8 +653,8 @@
       <c r="P2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" s="2" t="n">
-        <v>1</v>
+      <c r="Q2" t="n">
+        <v>0</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>1</v>
